--- a/Team-Data/2008-09/3-9-2008-09.xlsx
+++ b/Team-Data/2008-09/3-9-2008-09.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,22 +728,22 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E2" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F2" t="n">
         <v>28</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.556</v>
       </c>
       <c r="H2" t="n">
         <v>48.1</v>
       </c>
       <c r="I2" t="n">
-        <v>35.9</v>
+        <v>36</v>
       </c>
       <c r="J2" t="n">
         <v>78.7</v>
@@ -685,37 +752,37 @@
         <v>0.457</v>
       </c>
       <c r="L2" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="M2" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="N2" t="n">
-        <v>0.363</v>
+        <v>0.362</v>
       </c>
       <c r="O2" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="P2" t="n">
         <v>25.6</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.735</v>
+        <v>0.736</v>
       </c>
       <c r="R2" t="n">
         <v>10.6</v>
       </c>
       <c r="S2" t="n">
-        <v>29.4</v>
+        <v>29.3</v>
       </c>
       <c r="T2" t="n">
-        <v>40</v>
+        <v>39.9</v>
       </c>
       <c r="U2" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="V2" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="W2" t="n">
         <v>7.4</v>
@@ -727,19 +794,19 @@
         <v>4.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>19.5</v>
+        <v>19.7</v>
       </c>
       <c r="AA2" t="n">
         <v>20.7</v>
       </c>
       <c r="AB2" t="n">
-        <v>98</v>
+        <v>98.2</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AD2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AE2" t="n">
         <v>12</v>
@@ -757,10 +824,10 @@
         <v>22</v>
       </c>
       <c r="AJ2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AL2" t="n">
         <v>9</v>
@@ -769,7 +836,7 @@
         <v>7</v>
       </c>
       <c r="AN2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AO2" t="n">
         <v>18</v>
@@ -781,28 +848,28 @@
         <v>29</v>
       </c>
       <c r="AR2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AT2" t="n">
         <v>23</v>
       </c>
       <c r="AU2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AV2" t="n">
         <v>6</v>
       </c>
       <c r="AW2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY2" t="n">
         <v>11</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>15</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>10</v>
       </c>
       <c r="AZ2" t="n">
         <v>5</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-9-2008-09</t>
+          <t>2009-03-09</t>
         </is>
       </c>
     </row>
@@ -843,88 +910,88 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E3" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F3" t="n">
         <v>15</v>
       </c>
       <c r="G3" t="n">
-        <v>0.762</v>
+        <v>0.766</v>
       </c>
       <c r="H3" t="n">
         <v>48.4</v>
       </c>
       <c r="I3" t="n">
-        <v>37.5</v>
+        <v>37.4</v>
       </c>
       <c r="J3" t="n">
-        <v>77</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="K3" t="n">
         <v>0.487</v>
       </c>
       <c r="L3" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="M3" t="n">
         <v>16.5</v>
       </c>
       <c r="N3" t="n">
-        <v>0.393</v>
+        <v>0.39</v>
       </c>
       <c r="O3" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="P3" t="n">
-        <v>25.9</v>
+        <v>26</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.774</v>
+        <v>0.771</v>
       </c>
       <c r="R3" t="n">
         <v>10.6</v>
       </c>
       <c r="S3" t="n">
-        <v>31.9</v>
+        <v>31.8</v>
       </c>
       <c r="T3" t="n">
-        <v>42.5</v>
+        <v>42.4</v>
       </c>
       <c r="U3" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="V3" t="n">
         <v>15.8</v>
       </c>
       <c r="W3" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="X3" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Y3" t="n">
         <v>4.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="AA3" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="AB3" t="n">
-        <v>101.6</v>
+        <v>101.4</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD3" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AE3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF3" t="n">
         <v>3</v>
@@ -933,7 +1000,7 @@
         <v>3</v>
       </c>
       <c r="AH3" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AI3" t="n">
         <v>9</v>
@@ -951,22 +1018,22 @@
         <v>21</v>
       </c>
       <c r="AN3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AO3" t="n">
         <v>9</v>
       </c>
       <c r="AP3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AQ3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AR3" t="n">
         <v>20</v>
       </c>
       <c r="AS3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT3" t="n">
         <v>8</v>
@@ -981,7 +1048,7 @@
         <v>7</v>
       </c>
       <c r="AX3" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AY3" t="n">
         <v>12</v>
@@ -990,7 +1057,7 @@
         <v>27</v>
       </c>
       <c r="BA3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BB3" t="n">
         <v>9</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-9-2008-09</t>
+          <t>2009-03-09</t>
         </is>
       </c>
     </row>
@@ -1103,19 +1170,19 @@
         <v>-1.3</v>
       </c>
       <c r="AD4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE4" t="n">
+        <v>19</v>
+      </c>
+      <c r="AF4" t="n">
         <v>18</v>
       </c>
-      <c r="AF4" t="n">
-        <v>17</v>
-      </c>
       <c r="AG4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI4" t="n">
         <v>30</v>
@@ -1157,10 +1224,10 @@
         <v>12</v>
       </c>
       <c r="AV4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AW4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX4" t="n">
         <v>14</v>
@@ -1172,13 +1239,13 @@
         <v>20</v>
       </c>
       <c r="BA4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB4" t="n">
         <v>30</v>
       </c>
       <c r="BC4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-9-2008-09</t>
+          <t>2009-03-09</t>
         </is>
       </c>
     </row>
@@ -1210,82 +1277,82 @@
         <v>63</v>
       </c>
       <c r="E5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F5" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G5" t="n">
-        <v>0.444</v>
+        <v>0.46</v>
       </c>
       <c r="H5" t="n">
-        <v>48.7</v>
+        <v>48.6</v>
       </c>
       <c r="I5" t="n">
-        <v>37.7</v>
+        <v>37.6</v>
       </c>
       <c r="J5" t="n">
-        <v>83.59999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="K5" t="n">
-        <v>0.451</v>
+        <v>0.452</v>
       </c>
       <c r="L5" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="M5" t="n">
-        <v>15.6</v>
+        <v>15.5</v>
       </c>
       <c r="N5" t="n">
-        <v>0.381</v>
+        <v>0.377</v>
       </c>
       <c r="O5" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="P5" t="n">
-        <v>25</v>
+        <v>25.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.792</v>
+        <v>0.79</v>
       </c>
       <c r="R5" t="n">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="S5" t="n">
-        <v>30.5</v>
+        <v>30.4</v>
       </c>
       <c r="T5" t="n">
-        <v>42.7</v>
+        <v>42.6</v>
       </c>
       <c r="U5" t="n">
-        <v>20.9</v>
+        <v>21.1</v>
       </c>
       <c r="V5" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="W5" t="n">
         <v>7.5</v>
       </c>
       <c r="X5" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="AB5" t="n">
-        <v>101.2</v>
+        <v>100.9</v>
       </c>
       <c r="AC5" t="n">
-        <v>-1.3</v>
+        <v>-1.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE5" t="n">
         <v>18</v>
@@ -1294,19 +1361,19 @@
         <v>17</v>
       </c>
       <c r="AG5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AH5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AI5" t="n">
         <v>8</v>
       </c>
       <c r="AJ5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL5" t="n">
         <v>24</v>
@@ -1315,10 +1382,10 @@
         <v>24</v>
       </c>
       <c r="AN5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AO5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AP5" t="n">
         <v>14</v>
@@ -1327,7 +1394,7 @@
         <v>8</v>
       </c>
       <c r="AR5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AS5" t="n">
         <v>12</v>
@@ -1336,10 +1403,10 @@
         <v>7</v>
       </c>
       <c r="AU5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AV5" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AW5" t="n">
         <v>9</v>
@@ -1348,19 +1415,19 @@
         <v>4</v>
       </c>
       <c r="AY5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AZ5" t="n">
         <v>19</v>
       </c>
       <c r="BA5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BB5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-9-2008-09</t>
+          <t>2009-03-09</t>
         </is>
       </c>
     </row>
@@ -1389,49 +1456,49 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E6" t="n">
         <v>49</v>
       </c>
       <c r="F6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G6" t="n">
-        <v>0.803</v>
+        <v>0.79</v>
       </c>
       <c r="H6" t="n">
         <v>48.1</v>
       </c>
       <c r="I6" t="n">
-        <v>36.7</v>
+        <v>36.5</v>
       </c>
       <c r="J6" t="n">
-        <v>78</v>
+        <v>77.8</v>
       </c>
       <c r="K6" t="n">
         <v>0.47</v>
       </c>
       <c r="L6" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="M6" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="N6" t="n">
-        <v>0.395</v>
+        <v>0.393</v>
       </c>
       <c r="O6" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="P6" t="n">
-        <v>24.8</v>
+        <v>25</v>
       </c>
       <c r="Q6" t="n">
         <v>0.754</v>
       </c>
       <c r="R6" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="S6" t="n">
         <v>30.9</v>
@@ -1443,46 +1510,46 @@
         <v>20</v>
       </c>
       <c r="V6" t="n">
-        <v>13</v>
+        <v>13.2</v>
       </c>
       <c r="W6" t="n">
         <v>7.6</v>
       </c>
       <c r="X6" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Z6" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="AA6" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>100.1</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AD6" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="AE6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH6" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AI6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AJ6" t="n">
         <v>26</v>
@@ -1509,7 +1576,7 @@
         <v>23</v>
       </c>
       <c r="AR6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AS6" t="n">
         <v>10</v>
@@ -1521,7 +1588,7 @@
         <v>25</v>
       </c>
       <c r="AV6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AW6" t="n">
         <v>8</v>
@@ -1530,7 +1597,7 @@
         <v>6</v>
       </c>
       <c r="AY6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ6" t="n">
         <v>6</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-9-2008-09</t>
+          <t>2009-03-09</t>
         </is>
       </c>
     </row>
@@ -1649,19 +1716,19 @@
         <v>1.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE7" t="n">
         <v>11</v>
       </c>
       <c r="AF7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG7" t="n">
         <v>11</v>
       </c>
       <c r="AH7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AI7" t="n">
         <v>7</v>
@@ -1712,7 +1779,7 @@
         <v>7</v>
       </c>
       <c r="AY7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AZ7" t="n">
         <v>3</v>
@@ -1721,7 +1788,7 @@
         <v>24</v>
       </c>
       <c r="BB7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BC7" t="n">
         <v>11</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-9-2008-09</t>
+          <t>2009-03-09</t>
         </is>
       </c>
     </row>
@@ -1753,46 +1820,46 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E8" t="n">
         <v>40</v>
       </c>
       <c r="F8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G8" t="n">
-        <v>0.615</v>
+        <v>0.625</v>
       </c>
       <c r="H8" t="n">
         <v>48.2</v>
       </c>
       <c r="I8" t="n">
-        <v>36.6</v>
+        <v>36.7</v>
       </c>
       <c r="J8" t="n">
-        <v>78.7</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>0.465</v>
+        <v>0.467</v>
       </c>
       <c r="L8" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="M8" t="n">
         <v>17.6</v>
       </c>
       <c r="N8" t="n">
-        <v>0.362</v>
+        <v>0.361</v>
       </c>
       <c r="O8" t="n">
         <v>23</v>
       </c>
       <c r="P8" t="n">
-        <v>30.4</v>
+        <v>30.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.756</v>
+        <v>0.754</v>
       </c>
       <c r="R8" t="n">
         <v>10.9</v>
@@ -1801,10 +1868,10 @@
         <v>30.4</v>
       </c>
       <c r="T8" t="n">
-        <v>41.3</v>
+        <v>41.2</v>
       </c>
       <c r="U8" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="V8" t="n">
         <v>15.6</v>
@@ -1825,13 +1892,13 @@
         <v>23.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>102.6</v>
+        <v>102.7</v>
       </c>
       <c r="AC8" t="n">
         <v>2.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE8" t="n">
         <v>7</v>
@@ -1846,13 +1913,13 @@
         <v>25</v>
       </c>
       <c r="AI8" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AJ8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AL8" t="n">
         <v>19</v>
@@ -1861,7 +1928,7 @@
         <v>18</v>
       </c>
       <c r="AN8" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AO8" t="n">
         <v>1</v>
@@ -1876,7 +1943,7 @@
         <v>16</v>
       </c>
       <c r="AS8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AT8" t="n">
         <v>15</v>
@@ -1885,7 +1952,7 @@
         <v>8</v>
       </c>
       <c r="AV8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AW8" t="n">
         <v>3</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-9-2008-09</t>
+          <t>2009-03-09</t>
         </is>
       </c>
     </row>
@@ -1935,16 +2002,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E9" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F9" t="n">
         <v>30</v>
       </c>
       <c r="G9" t="n">
-        <v>0.516</v>
+        <v>0.508</v>
       </c>
       <c r="H9" t="n">
         <v>48.3</v>
@@ -1953,16 +2020,16 @@
         <v>35.9</v>
       </c>
       <c r="J9" t="n">
-        <v>79.2</v>
+        <v>79</v>
       </c>
       <c r="K9" t="n">
-        <v>0.453</v>
+        <v>0.454</v>
       </c>
       <c r="L9" t="n">
         <v>4.6</v>
       </c>
       <c r="M9" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="N9" t="n">
         <v>0.343</v>
@@ -1974,28 +2041,28 @@
         <v>22.8</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.749</v>
+        <v>0.752</v>
       </c>
       <c r="R9" t="n">
         <v>11</v>
       </c>
       <c r="S9" t="n">
-        <v>29.7</v>
+        <v>29.8</v>
       </c>
       <c r="T9" t="n">
         <v>40.7</v>
       </c>
       <c r="U9" t="n">
-        <v>20.4</v>
+        <v>20.2</v>
       </c>
       <c r="V9" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="W9" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="X9" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Y9" t="n">
         <v>4</v>
@@ -2007,13 +2074,13 @@
         <v>19.9</v>
       </c>
       <c r="AB9" t="n">
-        <v>93.5</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="AC9" t="n">
-        <v>-0.4</v>
+        <v>-0.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="AE9" t="n">
         <v>15</v>
@@ -2025,13 +2092,13 @@
         <v>15</v>
       </c>
       <c r="AH9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AJ9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK9" t="n">
         <v>18</v>
@@ -2046,16 +2113,16 @@
         <v>26</v>
       </c>
       <c r="AO9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AP9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AQ9" t="n">
         <v>25</v>
       </c>
       <c r="AR9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AS9" t="n">
         <v>17</v>
@@ -2073,7 +2140,7 @@
         <v>28</v>
       </c>
       <c r="AX9" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AY9" t="n">
         <v>5</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-9-2008-09</t>
+          <t>2009-03-09</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>-3.7</v>
       </c>
       <c r="AD10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE10" t="n">
         <v>24</v>
@@ -2216,7 +2283,7 @@
         <v>3</v>
       </c>
       <c r="AK10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AL10" t="n">
         <v>15</v>
@@ -2234,7 +2301,7 @@
         <v>2</v>
       </c>
       <c r="AQ10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-9-2008-09</t>
+          <t>2009-03-09</t>
         </is>
       </c>
     </row>
@@ -2299,16 +2366,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E11" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F11" t="n">
         <v>23</v>
       </c>
       <c r="G11" t="n">
-        <v>0.646</v>
+        <v>0.641</v>
       </c>
       <c r="H11" t="n">
         <v>48.2</v>
@@ -2320,34 +2387,34 @@
         <v>79.59999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>0.449</v>
+        <v>0.45</v>
       </c>
       <c r="L11" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="M11" t="n">
         <v>20.5</v>
       </c>
       <c r="N11" t="n">
-        <v>0.378</v>
+        <v>0.377</v>
       </c>
       <c r="O11" t="n">
         <v>19.5</v>
       </c>
       <c r="P11" t="n">
-        <v>24.3</v>
+        <v>24.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.805</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="R11" t="n">
         <v>10.5</v>
       </c>
       <c r="S11" t="n">
-        <v>32.5</v>
+        <v>32.4</v>
       </c>
       <c r="T11" t="n">
-        <v>43</v>
+        <v>42.9</v>
       </c>
       <c r="U11" t="n">
         <v>20.5</v>
@@ -2365,22 +2432,22 @@
         <v>5.4</v>
       </c>
       <c r="Z11" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="AA11" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="AB11" t="n">
-        <v>98.8</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="AC11" t="n">
         <v>3.9</v>
       </c>
       <c r="AD11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF11" t="n">
         <v>7</v>
@@ -2389,7 +2456,7 @@
         <v>6</v>
       </c>
       <c r="AH11" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI11" t="n">
         <v>26</v>
@@ -2398,7 +2465,7 @@
         <v>20</v>
       </c>
       <c r="AK11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL11" t="n">
         <v>7</v>
@@ -2407,7 +2474,7 @@
         <v>5</v>
       </c>
       <c r="AN11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AO11" t="n">
         <v>12</v>
@@ -2416,7 +2483,7 @@
         <v>19</v>
       </c>
       <c r="AQ11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AR11" t="n">
         <v>23</v>
@@ -2431,7 +2498,7 @@
         <v>16</v>
       </c>
       <c r="AV11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW11" t="n">
         <v>25</v>
@@ -2449,10 +2516,10 @@
         <v>14</v>
       </c>
       <c r="BB11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BC11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-9-2008-09</t>
+          <t>2009-03-09</t>
         </is>
       </c>
     </row>
@@ -2559,10 +2626,10 @@
         <v>-1.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF12" t="n">
         <v>21</v>
@@ -2580,7 +2647,7 @@
         <v>2</v>
       </c>
       <c r="AK12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AL12" t="n">
         <v>4</v>
@@ -2613,7 +2680,7 @@
         <v>5</v>
       </c>
       <c r="AV12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW12" t="n">
         <v>19</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-9-2008-09</t>
+          <t>2009-03-09</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>-8.699999999999999</v>
       </c>
       <c r="AD13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE13" t="n">
         <v>28</v>
@@ -2753,7 +2820,7 @@
         <v>28</v>
       </c>
       <c r="AH13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI13" t="n">
         <v>25</v>
@@ -2774,10 +2841,10 @@
         <v>23</v>
       </c>
       <c r="AO13" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AP13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AQ13" t="n">
         <v>27</v>
@@ -2786,13 +2853,13 @@
         <v>12</v>
       </c>
       <c r="AS13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AT13" t="n">
         <v>21</v>
       </c>
       <c r="AU13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AV13" t="n">
         <v>19</v>
@@ -2804,10 +2871,10 @@
         <v>2</v>
       </c>
       <c r="AY13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA13" t="n">
         <v>26</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-9-2008-09</t>
+          <t>2009-03-09</t>
         </is>
       </c>
     </row>
@@ -2848,13 +2915,13 @@
         <v>62</v>
       </c>
       <c r="E14" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G14" t="n">
-        <v>0.79</v>
+        <v>0.806</v>
       </c>
       <c r="H14" t="n">
         <v>48.3</v>
@@ -2872,28 +2939,28 @@
         <v>6.9</v>
       </c>
       <c r="M14" t="n">
-        <v>19.1</v>
+        <v>18.9</v>
       </c>
       <c r="N14" t="n">
-        <v>0.362</v>
+        <v>0.365</v>
       </c>
       <c r="O14" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="P14" t="n">
         <v>26.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.771</v>
+        <v>0.77</v>
       </c>
       <c r="R14" t="n">
-        <v>12.7</v>
+        <v>12.6</v>
       </c>
       <c r="S14" t="n">
-        <v>31.6</v>
+        <v>31.9</v>
       </c>
       <c r="T14" t="n">
-        <v>44.3</v>
+        <v>44.5</v>
       </c>
       <c r="U14" t="n">
         <v>23.7</v>
@@ -2905,34 +2972,34 @@
         <v>8.5</v>
       </c>
       <c r="X14" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Y14" t="n">
         <v>4.7</v>
       </c>
       <c r="Z14" t="n">
-        <v>20.8</v>
+        <v>20.6</v>
       </c>
       <c r="AA14" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="AB14" t="n">
         <v>108.7</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AD14" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AE14" t="n">
         <v>1</v>
       </c>
       <c r="AF14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH14" t="n">
         <v>15</v>
@@ -2947,13 +3014,13 @@
         <v>4</v>
       </c>
       <c r="AL14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AM14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AN14" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AO14" t="n">
         <v>5</v>
@@ -2968,7 +3035,7 @@
         <v>3</v>
       </c>
       <c r="AS14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT14" t="n">
         <v>1</v>
@@ -2989,10 +3056,10 @@
         <v>13</v>
       </c>
       <c r="AZ14" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BA14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB14" t="n">
         <v>1</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-9-2008-09</t>
+          <t>2009-03-09</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>-6</v>
       </c>
       <c r="AD15" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AE15" t="n">
         <v>27</v>
@@ -3147,7 +3214,7 @@
         <v>24</v>
       </c>
       <c r="AR15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS15" t="n">
         <v>28</v>
@@ -3168,10 +3235,10 @@
         <v>21</v>
       </c>
       <c r="AY15" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AZ15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA15" t="n">
         <v>9</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-9-2008-09</t>
+          <t>2009-03-09</t>
         </is>
       </c>
     </row>
@@ -3209,61 +3276,61 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E16" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F16" t="n">
         <v>29</v>
       </c>
       <c r="G16" t="n">
-        <v>0.54</v>
+        <v>0.532</v>
       </c>
       <c r="H16" t="n">
-        <v>48.4</v>
+        <v>48.2</v>
       </c>
       <c r="I16" t="n">
-        <v>37</v>
+        <v>36.9</v>
       </c>
       <c r="J16" t="n">
-        <v>81.2</v>
+        <v>81</v>
       </c>
       <c r="K16" t="n">
         <v>0.455</v>
       </c>
       <c r="L16" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="M16" t="n">
-        <v>19.7</v>
+        <v>19.5</v>
       </c>
       <c r="N16" t="n">
-        <v>0.354</v>
+        <v>0.352</v>
       </c>
       <c r="O16" t="n">
-        <v>17.1</v>
+        <v>16.9</v>
       </c>
       <c r="P16" t="n">
-        <v>22.5</v>
+        <v>22.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.761</v>
+        <v>0.758</v>
       </c>
       <c r="R16" t="n">
         <v>10.2</v>
       </c>
       <c r="S16" t="n">
-        <v>29</v>
+        <v>29.1</v>
       </c>
       <c r="T16" t="n">
-        <v>39.3</v>
+        <v>39.2</v>
       </c>
       <c r="U16" t="n">
         <v>20.1</v>
       </c>
       <c r="V16" t="n">
-        <v>12.7</v>
+        <v>12.6</v>
       </c>
       <c r="W16" t="n">
         <v>8.1</v>
@@ -3275,31 +3342,31 @@
         <v>4</v>
       </c>
       <c r="Z16" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="AB16" t="n">
-        <v>98</v>
+        <v>97.5</v>
       </c>
       <c r="AC16" t="n">
         <v>-0.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="AE16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AF16" t="n">
         <v>13</v>
       </c>
       <c r="AG16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AH16" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="AI16" t="n">
         <v>11</v>
@@ -3314,16 +3381,16 @@
         <v>11</v>
       </c>
       <c r="AM16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AN16" t="n">
         <v>22</v>
       </c>
       <c r="AO16" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AP16" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ16" t="n">
         <v>20</v>
@@ -3332,7 +3399,7 @@
         <v>24</v>
       </c>
       <c r="AS16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT16" t="n">
         <v>29</v>
@@ -3341,10 +3408,10 @@
         <v>23</v>
       </c>
       <c r="AV16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AX16" t="n">
         <v>5</v>
@@ -3353,13 +3420,13 @@
         <v>4</v>
       </c>
       <c r="AZ16" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="BA16" t="n">
         <v>28</v>
       </c>
       <c r="BB16" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BC16" t="n">
         <v>15</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-9-2008-09</t>
+          <t>2009-03-09</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E17" t="n">
         <v>30</v>
       </c>
       <c r="F17" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G17" t="n">
-        <v>0.462</v>
+        <v>0.455</v>
       </c>
       <c r="H17" t="n">
         <v>48.3</v>
@@ -3409,7 +3476,7 @@
         <v>36.7</v>
       </c>
       <c r="J17" t="n">
-        <v>82</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="K17" t="n">
         <v>0.448</v>
@@ -3421,13 +3488,13 @@
         <v>16.6</v>
       </c>
       <c r="N17" t="n">
-        <v>0.362</v>
+        <v>0.363</v>
       </c>
       <c r="O17" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="P17" t="n">
-        <v>26</v>
+        <v>25.9</v>
       </c>
       <c r="Q17" t="n">
         <v>0.783</v>
@@ -3436,10 +3503,10 @@
         <v>12.2</v>
       </c>
       <c r="S17" t="n">
-        <v>29.1</v>
+        <v>28.9</v>
       </c>
       <c r="T17" t="n">
-        <v>41.2</v>
+        <v>41.1</v>
       </c>
       <c r="U17" t="n">
         <v>21.6</v>
@@ -3448,7 +3515,7 @@
         <v>14.2</v>
       </c>
       <c r="W17" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="X17" t="n">
         <v>3.8</v>
@@ -3457,16 +3524,16 @@
         <v>4.8</v>
       </c>
       <c r="Z17" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="AA17" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="AB17" t="n">
-        <v>99.8</v>
+        <v>99.7</v>
       </c>
       <c r="AC17" t="n">
-        <v>-0.2</v>
+        <v>-0.4</v>
       </c>
       <c r="AD17" t="n">
         <v>1</v>
@@ -3475,16 +3542,16 @@
         <v>16</v>
       </c>
       <c r="AF17" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AG17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AH17" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI17" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AJ17" t="n">
         <v>9</v>
@@ -3499,22 +3566,22 @@
         <v>20</v>
       </c>
       <c r="AN17" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AO17" t="n">
         <v>7</v>
       </c>
       <c r="AP17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AS17" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AT17" t="n">
         <v>17</v>
@@ -3523,7 +3590,7 @@
         <v>9</v>
       </c>
       <c r="AV17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AW17" t="n">
         <v>13</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-9-2008-09</t>
+          <t>2009-03-09</t>
         </is>
       </c>
     </row>
@@ -3573,16 +3640,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E18" t="n">
         <v>18</v>
       </c>
       <c r="F18" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G18" t="n">
-        <v>0.286</v>
+        <v>0.29</v>
       </c>
       <c r="H18" t="n">
         <v>48.4</v>
@@ -3591,7 +3658,7 @@
         <v>36.8</v>
       </c>
       <c r="J18" t="n">
-        <v>83.59999999999999</v>
+        <v>83.5</v>
       </c>
       <c r="K18" t="n">
         <v>0.44</v>
@@ -3600,10 +3667,10 @@
         <v>6.2</v>
       </c>
       <c r="M18" t="n">
-        <v>18.3</v>
+        <v>18.2</v>
       </c>
       <c r="N18" t="n">
-        <v>0.341</v>
+        <v>0.342</v>
       </c>
       <c r="O18" t="n">
         <v>19</v>
@@ -3630,28 +3697,28 @@
         <v>14.4</v>
       </c>
       <c r="W18" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="X18" t="n">
         <v>4.1</v>
       </c>
       <c r="Y18" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="Z18" t="n">
         <v>22.1</v>
       </c>
       <c r="AA18" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="AB18" t="n">
         <v>98.8</v>
       </c>
       <c r="AC18" t="n">
-        <v>-5</v>
+        <v>-4.9</v>
       </c>
       <c r="AD18" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="AE18" t="n">
         <v>25</v>
@@ -3663,13 +3730,13 @@
         <v>25</v>
       </c>
       <c r="AH18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI18" t="n">
         <v>12</v>
       </c>
       <c r="AJ18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AK18" t="n">
         <v>29</v>
@@ -3690,7 +3757,7 @@
         <v>16</v>
       </c>
       <c r="AQ18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR18" t="n">
         <v>5</v>
@@ -3702,7 +3769,7 @@
         <v>11</v>
       </c>
       <c r="AU18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AV18" t="n">
         <v>16</v>
@@ -3717,13 +3784,13 @@
         <v>30</v>
       </c>
       <c r="AZ18" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA18" t="n">
         <v>22</v>
       </c>
-      <c r="BA18" t="n">
-        <v>23</v>
-      </c>
       <c r="BB18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BC18" t="n">
         <v>25</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-9-2008-09</t>
+          <t>2009-03-09</t>
         </is>
       </c>
     </row>
@@ -3833,16 +3900,16 @@
         <v>-2.2</v>
       </c>
       <c r="AD19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE19" t="n">
+        <v>19</v>
+      </c>
+      <c r="AF19" t="n">
         <v>18</v>
       </c>
-      <c r="AF19" t="n">
-        <v>17</v>
-      </c>
       <c r="AG19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH19" t="n">
         <v>7</v>
@@ -3875,10 +3942,10 @@
         <v>9</v>
       </c>
       <c r="AR19" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AS19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT19" t="n">
         <v>22</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-9-2008-09</t>
+          <t>2009-03-09</t>
         </is>
       </c>
     </row>
@@ -3937,16 +4004,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E20" t="n">
         <v>39</v>
       </c>
       <c r="F20" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G20" t="n">
-        <v>0.629</v>
+        <v>0.639</v>
       </c>
       <c r="H20" t="n">
         <v>48.1</v>
@@ -3958,25 +4025,25 @@
         <v>77</v>
       </c>
       <c r="K20" t="n">
-        <v>0.457</v>
+        <v>0.458</v>
       </c>
       <c r="L20" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="M20" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="N20" t="n">
-        <v>0.377</v>
+        <v>0.379</v>
       </c>
       <c r="O20" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="P20" t="n">
-        <v>22.9</v>
+        <v>23.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.805</v>
       </c>
       <c r="R20" t="n">
         <v>9.699999999999999</v>
@@ -4003,31 +4070,31 @@
         <v>3.6</v>
       </c>
       <c r="Z20" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="AB20" t="n">
-        <v>96.2</v>
+        <v>96.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="AD20" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="AE20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF20" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG20" t="n">
         <v>7</v>
       </c>
-      <c r="AG20" t="n">
-        <v>9</v>
-      </c>
       <c r="AH20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI20" t="n">
         <v>28</v>
@@ -4036,25 +4103,25 @@
         <v>28</v>
       </c>
       <c r="AK20" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AL20" t="n">
         <v>8</v>
       </c>
       <c r="AM20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AN20" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AO20" t="n">
+        <v>21</v>
+      </c>
+      <c r="AP20" t="n">
         <v>22</v>
       </c>
-      <c r="AP20" t="n">
-        <v>23</v>
-      </c>
       <c r="AQ20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AR20" t="n">
         <v>28</v>
@@ -4063,13 +4130,13 @@
         <v>16</v>
       </c>
       <c r="AT20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AU20" t="n">
         <v>26</v>
       </c>
       <c r="AV20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW20" t="n">
         <v>15</v>
@@ -4081,13 +4148,13 @@
         <v>1</v>
       </c>
       <c r="AZ20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BA20" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="BB20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BC20" t="n">
         <v>9</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-9-2008-09</t>
+          <t>2009-03-09</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>-2.2</v>
       </c>
       <c r="AD21" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AE21" t="n">
         <v>22</v>
@@ -4209,7 +4276,7 @@
         <v>22</v>
       </c>
       <c r="AH21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI21" t="n">
         <v>5</v>
@@ -4263,7 +4330,7 @@
         <v>23</v>
       </c>
       <c r="AZ21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA21" t="n">
         <v>29</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-9-2008-09</t>
+          <t>2009-03-09</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>-5.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE22" t="n">
         <v>26</v>
@@ -4391,16 +4458,16 @@
         <v>26</v>
       </c>
       <c r="AH22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AI22" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AJ22" t="n">
         <v>10</v>
       </c>
       <c r="AK22" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL22" t="n">
         <v>29</v>
@@ -4430,7 +4497,7 @@
         <v>3</v>
       </c>
       <c r="AU22" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AV22" t="n">
         <v>30</v>
@@ -4445,13 +4512,13 @@
         <v>18</v>
       </c>
       <c r="AZ22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA22" t="n">
         <v>19</v>
       </c>
       <c r="BB22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC22" t="n">
         <v>26</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-9-2008-09</t>
+          <t>2009-03-09</t>
         </is>
       </c>
     </row>
@@ -4483,25 +4550,25 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E23" t="n">
         <v>46</v>
       </c>
       <c r="F23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G23" t="n">
-        <v>0.73</v>
+        <v>0.742</v>
       </c>
       <c r="H23" t="n">
         <v>48.2</v>
       </c>
       <c r="I23" t="n">
-        <v>35.8</v>
+        <v>36</v>
       </c>
       <c r="J23" t="n">
-        <v>78</v>
+        <v>78.2</v>
       </c>
       <c r="K23" t="n">
         <v>0.46</v>
@@ -4510,28 +4577,28 @@
         <v>10.3</v>
       </c>
       <c r="M23" t="n">
-        <v>26.2</v>
+        <v>26.4</v>
       </c>
       <c r="N23" t="n">
         <v>0.391</v>
       </c>
       <c r="O23" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="P23" t="n">
-        <v>27.5</v>
+        <v>27.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.727</v>
+        <v>0.725</v>
       </c>
       <c r="R23" t="n">
-        <v>9.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="S23" t="n">
         <v>33</v>
       </c>
       <c r="T23" t="n">
-        <v>42.8</v>
+        <v>42.9</v>
       </c>
       <c r="U23" t="n">
         <v>19.2</v>
@@ -4555,13 +4622,13 @@
         <v>22.6</v>
       </c>
       <c r="AB23" t="n">
-        <v>102</v>
+        <v>102.1</v>
       </c>
       <c r="AC23" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="AD23" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="AE23" t="n">
         <v>4</v>
@@ -4576,7 +4643,7 @@
         <v>23</v>
       </c>
       <c r="AI23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AJ23" t="n">
         <v>25</v>
@@ -4591,10 +4658,10 @@
         <v>2</v>
       </c>
       <c r="AN23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AO23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AP23" t="n">
         <v>4</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-9-2008-09</t>
+          <t>2009-03-09</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>0.4</v>
       </c>
       <c r="AD24" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AE24" t="n">
         <v>16</v>
@@ -4800,7 +4867,7 @@
         <v>18</v>
       </c>
       <c r="AW24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AX24" t="n">
         <v>10</v>
@@ -4815,7 +4882,7 @@
         <v>10</v>
       </c>
       <c r="BB24" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BC24" t="n">
         <v>14</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-9-2008-09</t>
+          <t>2009-03-09</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>1.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE25" t="n">
         <v>13</v>
@@ -4937,7 +5004,7 @@
         <v>13</v>
       </c>
       <c r="AH25" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI25" t="n">
         <v>2</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-9-2008-09</t>
+          <t>2009-03-09</t>
         </is>
       </c>
     </row>
@@ -5032,25 +5099,25 @@
         <v>62</v>
       </c>
       <c r="E26" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G26" t="n">
-        <v>0.645</v>
+        <v>0.629</v>
       </c>
       <c r="H26" t="n">
         <v>48.3</v>
       </c>
       <c r="I26" t="n">
-        <v>36.8</v>
+        <v>36.6</v>
       </c>
       <c r="J26" t="n">
         <v>79.2</v>
       </c>
       <c r="K26" t="n">
-        <v>0.465</v>
+        <v>0.462</v>
       </c>
       <c r="L26" t="n">
         <v>7.2</v>
@@ -5062,13 +5129,13 @@
         <v>0.379</v>
       </c>
       <c r="O26" t="n">
-        <v>18.7</v>
+        <v>18.5</v>
       </c>
       <c r="P26" t="n">
-        <v>24.5</v>
+        <v>24.3</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.763</v>
+        <v>0.762</v>
       </c>
       <c r="R26" t="n">
         <v>13</v>
@@ -5080,7 +5147,7 @@
         <v>41.2</v>
       </c>
       <c r="U26" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="V26" t="n">
         <v>12.8</v>
@@ -5092,40 +5159,40 @@
         <v>4.7</v>
       </c>
       <c r="Y26" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="Z26" t="n">
         <v>20.7</v>
       </c>
       <c r="AA26" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="AB26" t="n">
-        <v>99.5</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="AD26" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AE26" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF26" t="n">
         <v>7</v>
       </c>
-      <c r="AF26" t="n">
-        <v>6</v>
-      </c>
       <c r="AG26" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AH26" t="n">
         <v>15</v>
       </c>
       <c r="AI26" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AJ26" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK26" t="n">
         <v>8</v>
@@ -5134,19 +5201,19 @@
         <v>10</v>
       </c>
       <c r="AM26" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AN26" t="n">
         <v>7</v>
       </c>
       <c r="AO26" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AP26" t="n">
         <v>18</v>
       </c>
       <c r="AQ26" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR26" t="n">
         <v>1</v>
@@ -5158,7 +5225,7 @@
         <v>16</v>
       </c>
       <c r="AU26" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AV26" t="n">
         <v>5</v>
@@ -5167,22 +5234,22 @@
         <v>26</v>
       </c>
       <c r="AX26" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AY26" t="n">
         <v>3</v>
       </c>
       <c r="AZ26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA26" t="n">
         <v>13</v>
       </c>
       <c r="BB26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BC26" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-9-2008-09</t>
+          <t>2009-03-09</t>
         </is>
       </c>
     </row>
@@ -5289,19 +5356,19 @@
         <v>-8.9</v>
       </c>
       <c r="AD27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE27" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AF27" t="n">
         <v>29</v>
       </c>
       <c r="AG27" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AH27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI27" t="n">
         <v>21</v>
@@ -5310,7 +5377,7 @@
         <v>13</v>
       </c>
       <c r="AK27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL27" t="n">
         <v>13</v>
@@ -5319,7 +5386,7 @@
         <v>14</v>
       </c>
       <c r="AN27" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AO27" t="n">
         <v>4</v>
@@ -5334,7 +5401,7 @@
         <v>27</v>
       </c>
       <c r="AS27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AT27" t="n">
         <v>30</v>
@@ -5349,7 +5416,7 @@
         <v>22</v>
       </c>
       <c r="AX27" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AY27" t="n">
         <v>20</v>
@@ -5361,7 +5428,7 @@
         <v>11</v>
       </c>
       <c r="BB27" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BC27" t="n">
         <v>30</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-9-2008-09</t>
+          <t>2009-03-09</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>4</v>
       </c>
       <c r="AD28" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AE28" t="n">
         <v>5</v>
@@ -5483,7 +5550,7 @@
         <v>5</v>
       </c>
       <c r="AH28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI28" t="n">
         <v>10</v>
@@ -5492,7 +5559,7 @@
         <v>18</v>
       </c>
       <c r="AK28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AL28" t="n">
         <v>5</v>
@@ -5501,7 +5568,7 @@
         <v>8</v>
       </c>
       <c r="AN28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO28" t="n">
         <v>30</v>
@@ -5543,10 +5610,10 @@
         <v>30</v>
       </c>
       <c r="BB28" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BC28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-9-2008-09</t>
+          <t>2009-03-09</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>-3.7</v>
       </c>
       <c r="AD29" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE29" t="n">
         <v>23</v>
@@ -5674,7 +5741,7 @@
         <v>19</v>
       </c>
       <c r="AK29" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AL29" t="n">
         <v>23</v>
@@ -5686,10 +5753,10 @@
         <v>13</v>
       </c>
       <c r="AO29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP29" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AQ29" t="n">
         <v>1</v>
@@ -5698,7 +5765,7 @@
         <v>29</v>
       </c>
       <c r="AS29" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AT29" t="n">
         <v>27</v>
@@ -5707,7 +5774,7 @@
         <v>7</v>
       </c>
       <c r="AV29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW29" t="n">
         <v>29</v>
@@ -5716,16 +5783,16 @@
         <v>13</v>
       </c>
       <c r="AY29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ29" t="n">
         <v>4</v>
       </c>
       <c r="BA29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB29" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BC29" t="n">
         <v>24</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-9-2008-09</t>
+          <t>2009-03-09</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5902,7 @@
         <v>4</v>
       </c>
       <c r="AD30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE30" t="n">
         <v>7</v>
@@ -5847,7 +5914,7 @@
         <v>8</v>
       </c>
       <c r="AH30" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI30" t="n">
         <v>6</v>
@@ -5874,7 +5941,7 @@
         <v>3</v>
       </c>
       <c r="AQ30" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR30" t="n">
         <v>9</v>
@@ -5910,7 +5977,7 @@
         <v>6</v>
       </c>
       <c r="BC30" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-9-2008-09</t>
+          <t>2009-03-09</t>
         </is>
       </c>
     </row>
@@ -5939,88 +6006,88 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E31" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F31" t="n">
         <v>49</v>
       </c>
       <c r="G31" t="n">
-        <v>0.234</v>
+        <v>0.222</v>
       </c>
       <c r="H31" t="n">
         <v>48.1</v>
       </c>
       <c r="I31" t="n">
-        <v>36.2</v>
+        <v>36.1</v>
       </c>
       <c r="J31" t="n">
-        <v>80.8</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>0.447</v>
+        <v>0.446</v>
       </c>
       <c r="L31" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="M31" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="N31" t="n">
-        <v>0.324</v>
+        <v>0.325</v>
       </c>
       <c r="O31" t="n">
-        <v>17.5</v>
+        <v>17.3</v>
       </c>
       <c r="P31" t="n">
-        <v>22.9</v>
+        <v>22.7</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.762</v>
+        <v>0.763</v>
       </c>
       <c r="R31" t="n">
         <v>11.7</v>
       </c>
       <c r="S31" t="n">
-        <v>28</v>
+        <v>27.9</v>
       </c>
       <c r="T31" t="n">
-        <v>39.7</v>
+        <v>39.6</v>
       </c>
       <c r="U31" t="n">
         <v>20.1</v>
       </c>
       <c r="V31" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="W31" t="n">
         <v>7.4</v>
       </c>
       <c r="X31" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Y31" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Z31" t="n">
         <v>20.5</v>
       </c>
       <c r="AA31" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="AB31" t="n">
-        <v>94.7</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="AC31" t="n">
-        <v>-7.5</v>
+        <v>-7.8</v>
       </c>
       <c r="AD31" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AE31" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AF31" t="n">
         <v>29</v>
@@ -6038,7 +6105,7 @@
         <v>12</v>
       </c>
       <c r="AK31" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL31" t="n">
         <v>25</v>
@@ -6053,10 +6120,10 @@
         <v>26</v>
       </c>
       <c r="AP31" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AQ31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AR31" t="n">
         <v>8</v>
@@ -6065,7 +6132,7 @@
         <v>30</v>
       </c>
       <c r="AT31" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AU31" t="n">
         <v>24</v>
@@ -6074,7 +6141,7 @@
         <v>12</v>
       </c>
       <c r="AW31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AX31" t="n">
         <v>25</v>
@@ -6083,7 +6150,7 @@
         <v>21</v>
       </c>
       <c r="AZ31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA31" t="n">
         <v>27</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-9-2008-09</t>
+          <t>2009-03-09</t>
         </is>
       </c>
     </row>
